--- a/data/publish_skills.xlsx
+++ b/data/publish_skills.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_A1AA029904802ABFF0F436C631EA8C2EE6AA7EBA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77B0B440-E845-4973-9228-B391134DE81D}"/>
+  <bookViews>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Publish Skills" state="visible" r:id="rId4"/>
+    <sheet name="Publish Skills" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>Slug</t>
   </si>
@@ -31,69 +35,67 @@
     <t>Changelog</t>
   </si>
   <si>
-    <t>text-summarizer</t>
-  </si>
-  <si>
-    <t>Text Summarizer</t>
-  </si>
-  <si>
-    <t>1.0.0</t>
-  </si>
-  <si>
-    <t>nlp, summarization, latest</t>
-  </si>
-  <si>
-    <t>D:\Yash Assignment\skills\text-summarizer</t>
-  </si>
-  <si>
-    <t>Initial release of text summarization skill.</t>
-  </si>
-  <si>
-    <t>image-classifier</t>
-  </si>
-  <si>
-    <t>Image Classifier</t>
-  </si>
-  <si>
-    <t>vision, classification, latest</t>
-  </si>
-  <si>
-    <t>D:\Yash Assignment\skills\image-classifier</t>
-  </si>
-  <si>
-    <t>Initial release of image classification skill.</t>
-  </si>
-  <si>
-    <t>code-reviewer</t>
-  </si>
-  <si>
-    <t>Code Reviewer</t>
-  </si>
-  <si>
-    <t>code, review, latest</t>
-  </si>
-  <si>
-    <t>D:\Yash Assignment\skills\code-reviewer</t>
-  </si>
-  <si>
-    <t>Initial release of automated code review skill.</t>
+    <t>P&amp;ID Equipment Recognition Skill</t>
+  </si>
+  <si>
+    <t>1.0.1</t>
+  </si>
+  <si>
+    <t>pid-equipment-recognition</t>
+  </si>
+  <si>
+    <t>shipping-and-launch-production-grade-engineering-skills</t>
+  </si>
+  <si>
+    <t>documentation-and-adrs-production-grade-engineering-skills</t>
+  </si>
+  <si>
+    <t>Documentation and ADRs Engineering skills</t>
+  </si>
+  <si>
+    <t>Shipping and Launch Engineering skills</t>
+  </si>
+  <si>
+    <t>latest</t>
+  </si>
+  <si>
+    <t>Ship with confidence. The goal is not just to deploy — it's to deploy safely, with monitoring in place, a rollback plan ready, and a clear understanding of what success looks like. Every launch should be reversible, observable, and incremental.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document explains the major components shown in the refinery Process and Instrumentation Diagram (P&amp;ID), along with the function of each item and the meaning of common instrument tags.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document decisions, not just code. The most valuable documentation captures the why — the context, constraints, and trade-offs that led to a decision. Code shows what was built; documentation explains why it was built this way and what alternatives were considered. This context is essential for future humans and agents working in the codebase.
+</t>
+  </si>
+  <si>
+    <t>D:\Yash Assignment\skill1</t>
+  </si>
+  <si>
+    <t>D:\Yash Assignment\skill2</t>
+  </si>
+  <si>
+    <t>D:\Yash Assignment\skill3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -118,23 +120,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,18 +487,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="1" max="1" width="37.21875" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,68 +518,68 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>